--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0071.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0071.xlsx
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đừng có mà thử thách sự kiên nhẫn của ta...</t>
+          <t>Đừng có mà thử thách sự kiên nhẫn của tao...</t>
         </is>
       </c>
     </row>
